--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_434_Libya.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_434_Libya.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rce6d1d7e78014f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R09c4497a40ed4eac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3c66ad220edc4f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf469b9ebd53d4d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R551710cf618c474c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R563d20ba65bf4c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R02dbacd9778c4f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7598c24f1eef4a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R881f9d33dd1c4962"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd675fef2f5f94ca2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R03934f26d8a24be7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R149f0d1d1090476d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ434CommercialTable" displayName="EEZ434CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ434CommercialTable" displayName="EEZ434CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ434FunctionalTable" displayName="EEZ434FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ434FunctionalTable" displayName="EEZ434FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ434ValidationTable" displayName="EEZ434ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ434ValidationTable" displayName="EEZ434ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10543,7 +10497,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc22ce04df97b42e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6269d6abbc904687"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10553,20 +10507,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10574,714 +10518,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>154.0864098901</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>154.0864098901</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$148,A2,'Species'!$U$2:$U$148))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>19850.174846292575</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>19850.174846292575</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1.925266245</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.061674996026328</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1152.590394779068</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1.925266245</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1281.3115775159874</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$148,A3,'Species'!$U$2:$U$148))</x:f>
-        <x:v>2466.8659295192315</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.061674996026328</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1152.590394779068</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2219.043381379364</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>247.82254813986765</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.111679902348651</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.111679902348651</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>892.7031155608</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.911781905995425</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>81.61724029678152</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>892.7031155608</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>114.58037495435399</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$148,A4,'Species'!$U$2:$U$148))</x:f>
-        <x:v>102286.25770387646</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.911781905995425</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>81.61724029678152</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>72859.96469641133</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>29426.293007465123</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.4038746536603042</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.4038746536603043</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>148.51102072900002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2184860386414673</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>165.3811618477378</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>148.51102072900002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>170.37414199520154</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$148,A5,'Species'!$U$2:$U$148))</x:f>
-        <x:v>25302.437733534967</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2184860386414673</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>165.3811618477378</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>24560.925155355493</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>741.5125781794741</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.030190742958141</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.030190742958140882</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>7560.8620535623995</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.7700656910970296</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>58.89327301952413</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>7560.8620535623995</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>58.90369418906894</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$148,A6,'Species'!$U$2:$U$148))</x:f>
-        <x:v>445362.7062087754</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.7700656910970296</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>58.89327301952413</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>445283.9131834103</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>78.79302536509931</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0001769500829298</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0001769500829297753</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.458565789</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.252763041466227</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>17.896291351867795</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.458565789</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>28.856307430634057</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$148,A7,'Species'!$U$2:$U$148))</x:f>
-        <x:v>13.232515384555269</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.252763041466227</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>17.896291351867795</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8.206626963943132</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>5.025888420612137</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6124182861843268</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6124182861843267</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>10662.502386982602</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4728979423124855</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>297.0967782638254</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>10662.502386982602</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>480.6727899919317</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$148,A8,'Species'!$U$2:$U$148))</x:f>
-        <x:v>5125174.770646559</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4728979423124855</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>297.0967782638254</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3167795.1074028793</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1957379.6632436798</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.6178997052774793</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.6178997052774793</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>18643.7305388342</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4613870951822654</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>289.32575505835706</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>18643.7305388342</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>643.9297463263916</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$148,A9,'Species'!$U$2:$U$148))</x:f>
-        <x:v>12005252.676449107</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4613870951822654</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>289.32575505835706</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>5394111.415252754</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>6611141.261196353</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.2256219332997538</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.225621933299754</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.061036241000000005</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.061036241000000005</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$148,A10,'Species'!$U$2:$U$148))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>13.66431229454516</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>13.66431229454516</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>315.9911427395</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9226362043305643</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>836.8280023283396</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>315.9911427395</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>841.6854526294297</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$148,A11,'Species'!$U$2:$U$148))</x:f>
-        <x:v>265965.1480035868</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9226362043305643</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>836.8280023283396</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>264430.236732145</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1534.911271441786</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0058045981821533</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0058045981821533395</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>5612.541422619199</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.15392657297013</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1425.3665836719485</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>5612.541422619199</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1522.163778243104</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$148,A12,'Species'!$U$2:$U$148))</x:f>
-        <x:v>8543207.257399965</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.15392657297013</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1425.3665836719485</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>7999928.993276025</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>543278.2641239399</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0679103857772447</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.06791038577724473</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>2072.0961174597</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.462901095841344</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2903.3613814647742</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>2072.0961174597</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2921.742606004766</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$148,A13,'Species'!$U$2:$U$148))</x:f>
-        <x:v>6054131.510119062</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.462901095841344</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2903.3613814647742</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>6016043.84611559</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>38087.664003471844</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0063310150287659</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.006331015028765806</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9760a1816b144f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e9fa8bbcd0c47e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11291,20 +10771,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11312,1416 +10782,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2178.6277780275004</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.120213113477942</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1318.903781591124</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2178.6277780275004</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1466.559671675837</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$148,A2,'Species'!$U$2:$U$148))</x:f>
-        <x:v>3195087.6388478694</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.120213113477942</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1318.903781591124</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2873400.415119938</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>321687.22372793127</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1119534966429327</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.11195349664293265</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3.517018202</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.874572516764586</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>749.1564392291509</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3.517018202</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>837.3328762773057</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$148,A3,'Species'!$U$2:$U$148))</x:f>
-        <x:v>2944.914967000298</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.874572516764586</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>749.1564392291509</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2634.7968329144305</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>310.1181340858675</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1177009666217173</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.11770096662171717</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>973.7315273181999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.176598822345937</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>150.17540863062413</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>973.7315273181999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1476.4858583789908</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$148,A4,'Species'!$U$2:$U$148))</x:f>
-        <x:v>1437700.8299430981</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.176598822345937</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>150.17540863062413</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>146230.53001153242</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1291470.2999315658</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>9.831741906629993</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>8.831741906629993</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1.185545872</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.166395534191526</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1466.8831983095968</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1.185545872</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1653.8508761067947</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$148,A5,'Species'!$U$2:$U$148))</x:f>
-        <x:v>1960.716079071994</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.166395534191526</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1466.8831983095968</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1739.0573204620998</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>221.65875860989422</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1274591446767237</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.1274591446767237</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.138620782</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.138620782</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$148,A6,'Species'!$U$2:$U$148))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>317.5618654851734</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>317.5618654851734</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3065.0023202118</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.4309387910043</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2697.3592427524113</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3065.0023202118</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2721.5104015757133</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$148,A7,'Species'!$U$2:$U$148))</x:f>
-        <x:v>8341435.695310108</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.4309387910043</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2697.3592427524113</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8267412.337480885</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>74023.35782922339</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0089536308106508</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.008953630810650799</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2.293435644</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.887288431115881</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>771.4156247784297</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2.293435644</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>883.8980757443423</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$148,A8,'Species'!$U$2:$U$148))</x:f>
-        <x:v>2027.1633525750867</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.887288431115881</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>771.4156247784297</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1769.1920902053803</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>257.97126236970644</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1458130317210267</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.14581303172102658</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1630.7480827511</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.361118160509568</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2296.77345689488</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1630.7480827511</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2523.3330725862866</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$148,A9,'Species'!$U$2:$U$148))</x:f>
-        <x:v>4114920.570262529</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.361118160509568</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2296.77345689488</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3745458.9113449412</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>369461.6589175877</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.098642560941863</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.09864256094186313</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5609.639850185201</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.154068095287498</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1425.831139546255</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5609.639850185201</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1522.510099075132</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$148,A10,'Species'!$U$2:$U$148))</x:f>
-        <x:v>8540733.32408128</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.154068095287498</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1425.831139546255</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>7998399.180033647</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>542334.1440476319</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0678053360229203</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.06780533602292033</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>10.829283718</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.870534762063753</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>74.22236048756918</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>10.829283718</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>74.30075920208523</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$148,A11,'Species'!$U$2:$U$148))</x:f>
-        <x:v>804.6240018621802</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.870534762063753</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>74.22236048756918</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>803.7749999395594</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.8490019226208005</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0010562681380792</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0010562681380792411</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>6.736435975999999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.409574663801422</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2567.8796394010656</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>6.736435975999999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2747.711587046706</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$148,A12,'Species'!$U$2:$U$148))</x:f>
-        <x:v>18509.783186653483</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.409574663801422</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2567.8796394010656</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>17298.356784899242</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1211.426401754241</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0700312993203935</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.07003129932039363</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.05078152</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.05078152</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$148,A13,'Species'!$U$2:$U$148))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>61.05281543181285</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>61.05281543181285</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>5762.420133545</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.406120071090373</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>254.753448203077</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>5762.420133545</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>327.0374241443225</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$148,A14,'Species'!$U$2:$U$148))</x:f>
-        <x:v>1884527.0373119395</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.406120071090373</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>254.753448203077</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1467996.399015424</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>416530.63829651545</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2837409128359443</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2837409128359442</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>15060.606704269601</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.246407478762785</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>176.36300042052986</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>15060.606704269601</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>188.14142586426348</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$148,A15,'Species'!$U$2:$U$148))</x:f>
-        <x:v>2833524.019722169</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.246407478762785</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>176.36300042052986</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2656133.7865185346</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>177390.23320363415</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0667851273546518</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.06678512735465192</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2436.0056832884</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.7359786480734414</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>544.4758832302222</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2436.0056832884</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>629.6138678746805</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$148,A16,'Species'!$U$2:$U$148))</x:f>
-        <x:v>1533742.9604199138</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.7359786480734414</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>544.4758832302222</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1326346.3459622925</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>207396.61445762124</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1563668608044837</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.1563668608044836</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>218.12828573049998</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.003260918957108</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>10.075368031776367</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>218.12828573049998</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>10.985800987117013</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$148,A17,'Species'!$U$2:$U$148))</x:f>
-        <x:v>2396.3139366962687</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.003260918957108</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>10.075368031776367</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2197.7227568752605</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>198.59117982100815</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0903622530183774</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.09036225301837737</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>20.466957551999997</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.005786205015529</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.134123791154446</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>20.466957551999997</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.426559615764809</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$148,A18,'Species'!$U$2:$U$148))</x:f>
-        <x:v>213.39995306925576</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.005786205015529</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.134123791154446</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>207.4146814602713</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>5.985271608984448</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0288565475059241</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.028856547505924167</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>881.8738318428</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.912288414985787</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>81.71248438577528</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>881.8738318428</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>115.07500283793891</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$148,A19,'Species'!$U$2:$U$148))</x:f>
-        <x:v>101481.63370201427</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.912288414985787</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>81.71248438577528</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>72060.10171467862</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>29421.53198733565</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.4082915689437958</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.40829156894379587</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>326.2601412319</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.380122931572728</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>239.95120297515908</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>326.2601412319</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>239.97626246899986</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$148,A20,'Species'!$U$2:$U$148))</x:f>
-        <x:v>78294.6892854394</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.380122931572728</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>239.95120297515908</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>78286.5133714397</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>8.175913999701152</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.000104435791653</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.00010443579165302143</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>11.963536976</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.520767711221056</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>331.7169863956462</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>11.963536976</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>627.4919410309934</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$148,A21,'Species'!$U$2:$U$148))</x:f>
-        <x:v>7507.0230386663015</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.520767711221056</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>331.7169863956462</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>3968.508432311602</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>3538.5146063546995</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.8916485038923208</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.8916485038923209</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>7715.6877751525</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>2.7768955569829767</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>59.82677009968499</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>7715.6877751525</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>60.30960137625767</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$148,A22,'Species'!$U$2:$U$148))</x:f>
-        <x:v>465330.05406311166</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>2.7768955569829767</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>59.82677009968499</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>461604.6786849986</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>3725.3753781130654</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0080704887756462</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.008070488775646228</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>0.574810119</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>0.574810119</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$148,A23,'Species'!$U$2:$U$148))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>74.04988781104268</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>74.04988781104268</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>148.37239994700002</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.2174195494693305</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>164.97553654117388</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>148.37239994700002</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>168.39301566177144</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$148,A24,'Species'!$U$2:$U$148))</x:f>
-        <x:v>24984.875868049792</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.2174195494693305</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>164.97553654117388</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>24477.816289157967</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>507.05957889182537</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0207150659561253</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.020715065956125295</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>0.080825986</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.8799999999999994</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>758.5775750291828</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>0.080825986</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>758.5775750291835</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$148,A25,'Species'!$U$2:$U$148))</x:f>
-        <x:v>61.31278045922274</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.8799999999999994</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>758.5775750291828</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>61.31278045922268</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>6.394884621840902e-14</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>1.0429937402845318e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>0.527310804</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.850061326792007</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>708.0457605782133</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>0.527310804</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>730.9867022008218</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$148,A26,'Species'!$U$2:$U$148))</x:f>
-        <x:v>385.4571856508239</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.850061326792007</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>708.0457605782133</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>373.3601792792891</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>12.097006371534746</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0324003657671421</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.03240036576714218</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7756636c71ee4474"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb64857e6ac84abd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12896,7 +11447,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12995,7 +11546,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>32589026.701867957</x:v>
+        <x:v>23407105.4909815</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13009,7 +11560,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>32589026.70186796</x:v>
+        <x:v>29149313.176975008</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13023,7 +11574,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-9181921.210886456</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13037,7 +11588,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-3439713.5248929486</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13048,9 +11599,9 @@
         <x:v>EEZ_434</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13062,47 +11613,19 @@
         <x:v>EEZ_434</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_434</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_434</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34ef9e98a9984b6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41ec21bf1eab4c25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13149,7 +11672,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
